--- a/UConnBleedBlue/wwwroot/players/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/players/Players.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\players\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08EA319C-A865-452F-B0FC-99E2381405A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D46021-6A1F-4827-9A57-B259FE8E885E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
+    <workbookView xWindow="18255" yWindow="2025" windowWidth="10350" windowHeight="13455" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -117,19 +117,28 @@
   </si>
   <si>
     <t>Mofsowitz, Marc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correia, Mark </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -152,11 +161,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -175,9 +185,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -215,7 +225,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -321,7 +331,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -463,7 +473,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -471,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -556,11 +566,11 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>16</v>
+      <c r="A8" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B8" s="1">
-        <v>1964</v>
+        <v>1982</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
@@ -568,10 +578,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -579,10 +589,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="B10" s="1">
-        <v>1979</v>
+        <v>1969</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -590,10 +600,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1">
-        <v>1971</v>
+        <v>1979</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
@@ -601,10 +611,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B12" s="1">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="C12" t="b">
         <v>1</v>
@@ -612,10 +622,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1972</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -623,10 +633,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1">
-        <v>1987</v>
+        <v>1979</v>
       </c>
       <c r="C14" t="b">
         <v>1</v>
@@ -634,10 +644,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B15" s="1">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="C15" t="b">
         <v>1</v>
@@ -645,10 +655,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1">
-        <v>1979</v>
+        <v>1986</v>
       </c>
       <c r="C16" t="b">
         <v>1</v>
@@ -656,10 +666,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1">
-        <v>1970</v>
+        <v>1979</v>
       </c>
       <c r="C17" t="b">
         <v>1</v>
@@ -667,10 +677,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1970</v>
       </c>
       <c r="C18" t="b">
         <v>1</v>
@@ -678,10 +688,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B19" s="1">
-        <v>1969</v>
+        <v>2015</v>
       </c>
       <c r="C19" t="b">
         <v>1</v>
@@ -689,10 +699,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B20" s="1">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="C20" t="b">
         <v>1</v>
@@ -700,10 +710,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1971</v>
       </c>
       <c r="C21" t="b">
         <v>1</v>
@@ -711,10 +721,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1970</v>
+        <v>12</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C22" t="b">
         <v>1</v>
@@ -722,10 +732,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1">
-        <v>1975</v>
+        <v>1970</v>
       </c>
       <c r="C23" t="b">
         <v>1</v>
@@ -733,10 +743,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1">
-        <v>1969</v>
+        <v>1975</v>
       </c>
       <c r="C24" t="b">
         <v>1</v>
@@ -744,10 +754,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1969</v>
       </c>
       <c r="C25" t="b">
         <v>1</v>
@@ -755,12 +765,23 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B27" s="1">
         <v>1979</v>
       </c>
-      <c r="C26" t="b">
+      <c r="C27" t="b">
         <v>1</v>
       </c>
     </row>

--- a/UConnBleedBlue/wwwroot/players/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/players/Players.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\players\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D46021-6A1F-4827-9A57-B259FE8E885E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9B2D88-1EFD-48BD-A5AA-A2B5035BFE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18255" yWindow="2025" windowWidth="10350" windowHeight="13455" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t xml:space="preserve">Correia, Mark </t>
+  </si>
+  <si>
+    <t>Ludwig, Mike</t>
   </si>
 </sst>
 </file>
@@ -185,9 +188,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -225,7 +228,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -331,7 +334,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -473,7 +476,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -481,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -644,10 +647,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="B15" s="1">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="C15" t="b">
         <v>1</v>
@@ -655,10 +658,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B16" s="1">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="C16" t="b">
         <v>1</v>
@@ -666,10 +669,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1">
-        <v>1979</v>
+        <v>1986</v>
       </c>
       <c r="C17" t="b">
         <v>1</v>
@@ -677,10 +680,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1">
-        <v>1970</v>
+        <v>1979</v>
       </c>
       <c r="C18" t="b">
         <v>1</v>
@@ -688,10 +691,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B19" s="1">
-        <v>2015</v>
+        <v>1970</v>
       </c>
       <c r="C19" t="b">
         <v>1</v>
@@ -699,10 +702,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B20" s="1">
-        <v>1969</v>
+        <v>2015</v>
       </c>
       <c r="C20" t="b">
         <v>1</v>
@@ -710,10 +713,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B21" s="1">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="C21" t="b">
         <v>1</v>
@@ -721,10 +724,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1971</v>
       </c>
       <c r="C22" t="b">
         <v>1</v>
@@ -732,10 +735,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1970</v>
+        <v>12</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C23" t="b">
         <v>1</v>
@@ -743,10 +746,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1">
-        <v>1975</v>
+        <v>1970</v>
       </c>
       <c r="C24" t="b">
         <v>1</v>
@@ -754,10 +757,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B25" s="1">
-        <v>1969</v>
+        <v>1975</v>
       </c>
       <c r="C25" t="b">
         <v>1</v>
@@ -765,10 +768,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1969</v>
       </c>
       <c r="C26" t="b">
         <v>1</v>
@@ -776,12 +779,23 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B28" s="1">
         <v>1979</v>
       </c>
-      <c r="C27" t="b">
+      <c r="C28" t="b">
         <v>1</v>
       </c>
     </row>

--- a/UConnBleedBlue/wwwroot/players/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/players/Players.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\players\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9B2D88-1EFD-48BD-A5AA-A2B5035BFE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED75F1D-96BA-4F77-849F-5CCB32C65D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -123,13 +123,97 @@
   </si>
   <si>
     <t>Ludwig, Mike</t>
+  </si>
+  <si>
+    <t>cjapar@me.com</t>
+  </si>
+  <si>
+    <t>Braswell, Robert</t>
+  </si>
+  <si>
+    <t>Rxbras@gmail.com</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Attending</t>
+  </si>
+  <si>
+    <t>Volunteer</t>
+  </si>
+  <si>
+    <t>Pavasaris, Cris</t>
+  </si>
+  <si>
+    <t>christopher.pavasaris@gmail.com</t>
+  </si>
+  <si>
+    <t>Reed, Hank</t>
+  </si>
+  <si>
+    <t>hll.reed01@gmail.com</t>
+  </si>
+  <si>
+    <t>Simon, Adam</t>
+  </si>
+  <si>
+    <t>adam@odysseyteencamp.com</t>
+  </si>
+  <si>
+    <t>Estep, EJ</t>
+  </si>
+  <si>
+    <t>michael.estep@acps.k12.va.us</t>
+  </si>
+  <si>
+    <t>Stowell, Bob</t>
+  </si>
+  <si>
+    <t>1photodog@gmail.com</t>
+  </si>
+  <si>
+    <t>artchristiani@gmail.com</t>
+  </si>
+  <si>
+    <t>Morgan, Jim</t>
+  </si>
+  <si>
+    <t>Jlmorgan3@icloud.com</t>
+  </si>
+  <si>
+    <t>npisciottano@hotmail.com</t>
+  </si>
+  <si>
+    <t>Carignan, Brad</t>
+  </si>
+  <si>
+    <t>bcarignan85@gmail.com</t>
+  </si>
+  <si>
+    <t>Worley, Martha</t>
+  </si>
+  <si>
+    <t>martha529@aol.com</t>
+  </si>
+  <si>
+    <t>aakowitz@aol.com</t>
+  </si>
+  <si>
+    <t>bickeldrew@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +226,22 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,17 +261,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -484,323 +591,501 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="1">
         <v>1971</v>
       </c>
-      <c r="C1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="1">
         <v>1967</v>
       </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1">
+      <c r="C4" s="1">
         <v>1970</v>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1">
+      <c r="C5" s="1">
         <v>1981</v>
       </c>
-      <c r="C4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="1">
         <v>1970</v>
       </c>
-      <c r="C5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1989</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B11" s="2"/>
+      <c r="C11" s="1">
         <v>1982</v>
       </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1">
+      <c r="C12" s="1">
         <v>1964</v>
       </c>
-      <c r="C9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="1">
+      <c r="C13" s="1">
         <v>1969</v>
       </c>
-      <c r="C10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="1">
+      <c r="C15" s="1">
         <v>1979</v>
       </c>
-      <c r="C11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="1">
+      <c r="C16" s="1">
         <v>1971</v>
       </c>
-      <c r="C12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="1">
+      <c r="C17" s="1">
         <v>1972</v>
       </c>
-      <c r="C13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="1">
+      <c r="C18" s="1">
         <v>1979</v>
       </c>
-      <c r="C14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1">
+      <c r="C19" s="1">
         <v>1982</v>
       </c>
-      <c r="C15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="1">
+      <c r="C20" s="1">
         <v>1987</v>
       </c>
-      <c r="C16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1">
+      <c r="C21" s="1">
         <v>1986</v>
       </c>
-      <c r="C17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1966</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="1">
+      <c r="C23" s="1">
         <v>1979</v>
       </c>
-      <c r="C18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="1">
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1">
         <v>1970</v>
       </c>
-      <c r="C19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="1">
+      <c r="C25" s="1">
         <v>2015</v>
       </c>
-      <c r="C20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="1">
+      <c r="C26" s="1">
         <v>1969</v>
       </c>
-      <c r="C21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="1">
         <v>1971</v>
       </c>
-      <c r="C22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="1">
+      <c r="C31" s="1">
         <v>1970</v>
       </c>
-      <c r="C24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="1">
+      <c r="C32" s="1">
         <v>1975</v>
       </c>
-      <c r="C25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="1">
+      <c r="C35" s="1">
         <v>1969</v>
       </c>
-      <c r="C26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="1">
+      <c r="C37" s="1">
         <v>1979</v>
       </c>
-      <c r="C28" t="b">
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D38" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
+    <hyperlink ref="B8" r:id="rId2" display="mailto:Rxbras@gmail.com" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
+    <hyperlink ref="B29" r:id="rId3" display="mailto:christopher.pavasaris@gmail.com" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
+    <hyperlink ref="B30" r:id="rId4" display="mailto:hll.reed01@gmail.com" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
+    <hyperlink ref="B33" r:id="rId5" display="mailto:adam@odysseyteencamp.com" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
+    <hyperlink ref="B14" r:id="rId6" display="mailto:michael.estep@acps.k12.va.us" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
+    <hyperlink ref="B34" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
+    <hyperlink ref="B10" r:id="rId8" display="mailto:artchristiani@gmail.com" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
+    <hyperlink ref="B22" r:id="rId9" display="mailto:Jlmorgan3@icloud.com" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
+    <hyperlink ref="B27" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
+    <hyperlink ref="B9" r:id="rId11" display="mailto:bcarignan85@gmail.com" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
+    <hyperlink ref="B38" r:id="rId12" display="mailto:martha529@aol.com" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
--- a/UConnBleedBlue/wwwroot/players/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/players/Players.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\players\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED75F1D-96BA-4F77-849F-5CCB32C65D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AF074A-E916-46B9-B1C4-74089F55E6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -207,6 +207,39 @@
   </si>
   <si>
     <t>bickeldrew@gmail.com</t>
+  </si>
+  <si>
+    <t>Ward, Jason</t>
+  </si>
+  <si>
+    <t>jason.derek.ward@gmail.com</t>
+  </si>
+  <si>
+    <t>Abare, Lou</t>
+  </si>
+  <si>
+    <t>louabare@yahoo.com</t>
+  </si>
+  <si>
+    <t>Casarella, Tony</t>
+  </si>
+  <si>
+    <t>elizabeth.casarella@gmail.com</t>
+  </si>
+  <si>
+    <t>paul@levelbreaker.com</t>
+  </si>
+  <si>
+    <t>Konecny, Jon</t>
+  </si>
+  <si>
+    <t>Drjpkonecny@gmail.com</t>
+  </si>
+  <si>
+    <t>O'Connel, Dennis</t>
+  </si>
+  <si>
+    <t>dennis.p.oconnell@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -591,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -619,13 +652,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>55</v>
+        <v>59</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C2" s="1">
-        <v>1971</v>
+        <v>1977</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -633,13 +666,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>29</v>
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
       </c>
       <c r="C3" s="1">
-        <v>1967</v>
+        <v>1971</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -647,10 +680,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C4" s="1">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -658,10 +694,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
-        <v>1981</v>
+        <v>1970</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -669,13 +705,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -683,10 +716,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1970</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -694,10 +730,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>21</v>
@@ -705,45 +738,47 @@
       <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1989</v>
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1989</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="2"/>
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="C11" s="1">
-        <v>1982</v>
+        <v>1969</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -751,21 +786,25 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1964</v>
+        <v>6</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>0</v>
-      </c>
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="2"/>
       <c r="C13" s="1">
-        <v>1969</v>
+        <v>1982</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -773,13 +812,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1964</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
@@ -787,10 +823,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C15" s="1">
-        <v>1979</v>
+        <v>1969</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
@@ -798,10 +834,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1971</v>
+        <v>43</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
@@ -809,10 +848,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1">
-        <v>1972</v>
+        <v>1979</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
@@ -820,10 +859,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C18" s="1">
-        <v>1979</v>
+        <v>1971</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
@@ -831,10 +870,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1">
-        <v>1982</v>
+        <v>1972</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
@@ -842,21 +881,24 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>64</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C20" s="1">
-        <v>1987</v>
+        <v>1979</v>
       </c>
       <c r="D20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C21" s="1">
-        <v>1986</v>
+        <v>1979</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
@@ -864,13 +906,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1">
-        <v>1966</v>
+        <v>1982</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
@@ -878,10 +917,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C23" s="1">
-        <v>1979</v>
+        <v>1987</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
@@ -889,10 +928,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1">
-        <v>1970</v>
+        <v>1986</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
@@ -900,10 +939,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>48</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="C25" s="1">
-        <v>2015</v>
+        <v>1966</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
@@ -911,10 +953,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C26" s="1">
-        <v>1969</v>
+        <v>1979</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
@@ -922,13 +964,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C27" s="1">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
@@ -936,10 +975,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2015</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
@@ -947,13 +986,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>21</v>
+        <v>67</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1978</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
@@ -961,13 +1000,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1969</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
@@ -975,10 +1011,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="C31" s="1">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
@@ -986,10 +1025,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="1">
-        <v>1975</v>
+        <v>12</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
@@ -997,10 +1036,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>21</v>
@@ -1011,13 +1050,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="1">
-        <v>1970</v>
+        <v>40</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D34" t="b">
         <v>1</v>
@@ -1025,10 +1064,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D35" t="b">
         <v>1</v>
@@ -1036,10 +1075,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1975</v>
       </c>
       <c r="D36" t="b">
         <v>1</v>
@@ -1047,10 +1089,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1979</v>
+        <v>41</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D37" t="b">
         <v>1</v>
@@ -1058,34 +1103,101 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1969</v>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>53</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C43" s="1">
         <v>1975</v>
       </c>
-      <c r="D38" t="b">
+      <c r="D43" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
-    <hyperlink ref="B8" r:id="rId2" display="mailto:Rxbras@gmail.com" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
-    <hyperlink ref="B29" r:id="rId3" display="mailto:christopher.pavasaris@gmail.com" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
-    <hyperlink ref="B30" r:id="rId4" display="mailto:hll.reed01@gmail.com" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
-    <hyperlink ref="B33" r:id="rId5" display="mailto:adam@odysseyteencamp.com" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
-    <hyperlink ref="B14" r:id="rId6" display="mailto:michael.estep@acps.k12.va.us" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
-    <hyperlink ref="B34" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
-    <hyperlink ref="B10" r:id="rId8" display="mailto:artchristiani@gmail.com" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
-    <hyperlink ref="B22" r:id="rId9" display="mailto:Jlmorgan3@icloud.com" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
-    <hyperlink ref="B27" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
-    <hyperlink ref="B9" r:id="rId11" display="mailto:bcarignan85@gmail.com" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
-    <hyperlink ref="B38" r:id="rId12" display="mailto:martha529@aol.com" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
+    <hyperlink ref="B9" r:id="rId2" display="mailto:Rxbras@gmail.com" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
+    <hyperlink ref="B33" r:id="rId3" display="mailto:christopher.pavasaris@gmail.com" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
+    <hyperlink ref="B34" r:id="rId4" display="mailto:hll.reed01@gmail.com" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
+    <hyperlink ref="B37" r:id="rId5" display="mailto:adam@odysseyteencamp.com" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
+    <hyperlink ref="B16" r:id="rId6" display="mailto:michael.estep@acps.k12.va.us" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
+    <hyperlink ref="B38" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
+    <hyperlink ref="B12" r:id="rId8" display="mailto:artchristiani@gmail.com" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
+    <hyperlink ref="B25" r:id="rId9" display="mailto:Jlmorgan3@icloud.com" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
+    <hyperlink ref="B31" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
+    <hyperlink ref="B10" r:id="rId11" display="mailto:bcarignan85@gmail.com" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
+    <hyperlink ref="B43" r:id="rId12" display="mailto:martha529@aol.com" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+    <hyperlink ref="B42" r:id="rId13" display="mailto:jason.derek.ward@gmail.com" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
+    <hyperlink ref="B2" r:id="rId14" display="mailto:louabare@yahoo.com" xr:uid="{8869974B-11E2-4A99-8438-9F9B8ABEB9F6}"/>
+    <hyperlink ref="B11" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
+    <hyperlink ref="B36" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
+    <hyperlink ref="B20" r:id="rId17" display="mailto:Drjpkonecny@gmail.com" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
+    <hyperlink ref="B29" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId13"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
--- a/UConnBleedBlue/wwwroot/players/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/players/Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\players\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AF074A-E916-46B9-B1C4-74089F55E6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391DE659-D108-454A-A60E-0B8F84E79AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -240,6 +240,144 @@
   </si>
   <si>
     <t>dennis.p.oconnell@gmail.com</t>
+  </si>
+  <si>
+    <t>Nesteruk, Warren</t>
+  </si>
+  <si>
+    <t>hef714@aol.com</t>
+  </si>
+  <si>
+    <t>O'Roark, Mike</t>
+  </si>
+  <si>
+    <t>mikeoroark23@gmail.com</t>
+  </si>
+  <si>
+    <t>Henrich, Joe</t>
+  </si>
+  <si>
+    <t>jhenrich1972@gmail.com</t>
+  </si>
+  <si>
+    <t>Torre, Joe</t>
+  </si>
+  <si>
+    <t>jtorre2829@gmail.com</t>
+  </si>
+  <si>
+    <t>Mack, Gary</t>
+  </si>
+  <si>
+    <t>g.mack96@yahoo.com</t>
+  </si>
+  <si>
+    <t>Marrus, Glenn</t>
+  </si>
+  <si>
+    <t>Gjhusky52@yahoo.com</t>
+  </si>
+  <si>
+    <t>s.vibberts@yahoo.com</t>
+  </si>
+  <si>
+    <t>oldparsonage3@gmail.com</t>
+  </si>
+  <si>
+    <t>Petrillo, Peter</t>
+  </si>
+  <si>
+    <t>Lane, Peter</t>
+  </si>
+  <si>
+    <t>Peterlane@optonline.net</t>
+  </si>
+  <si>
+    <t>Anglim, Patrick</t>
+  </si>
+  <si>
+    <t>patrick@drpflexpak.com</t>
+  </si>
+  <si>
+    <t>Berry, Craig</t>
+  </si>
+  <si>
+    <t>cwb84122@gmail.com</t>
+  </si>
+  <si>
+    <t>Myers, Norm</t>
+  </si>
+  <si>
+    <t>Npmyers@sbcglobal.net</t>
+  </si>
+  <si>
+    <t>timarmour.ycn@gmail.com</t>
+  </si>
+  <si>
+    <t>shbrann52@gmail.com</t>
+  </si>
+  <si>
+    <t>coachcorreia7@gmail.com</t>
+  </si>
+  <si>
+    <t>cordseller1@gmail.com</t>
+  </si>
+  <si>
+    <t>kpdemers073@gmail.com</t>
+  </si>
+  <si>
+    <t>marksflood1@gmail.com</t>
+  </si>
+  <si>
+    <t>gragmgorski@yahoo.com</t>
+  </si>
+  <si>
+    <t>robertinnis@yahoo.com</t>
+  </si>
+  <si>
+    <t>plamagna1@nefitness.com</t>
+  </si>
+  <si>
+    <t>mludwig67@optonline.net</t>
+  </si>
+  <si>
+    <t>pmargiatto66@gmail.com</t>
+  </si>
+  <si>
+    <t>marcmof@me.com</t>
+  </si>
+  <si>
+    <t>tomjney@yahoo.com</t>
+  </si>
+  <si>
+    <t>Miller, Ken</t>
+  </si>
+  <si>
+    <t>Kmills8080@gmail.com</t>
+  </si>
+  <si>
+    <t>bobnichols49@gmail.com</t>
+  </si>
+  <si>
+    <t>pnwokeji@hotmail.com</t>
+  </si>
+  <si>
+    <t>jpass33@earthlink.net</t>
+  </si>
+  <si>
+    <t>craigprimiani@aol.com</t>
+  </si>
+  <si>
+    <t>rick.robustelli@gmail.com</t>
+  </si>
+  <si>
+    <t>ralphtiner83@gmail.com</t>
+  </si>
+  <si>
+    <t>Murphy, Dan</t>
+  </si>
+  <si>
+    <t>Dmurphy287@charter.net</t>
   </si>
 </sst>
 </file>
@@ -624,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -694,10 +832,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>85</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="C5" s="1">
-        <v>1970</v>
+        <v>1987</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -705,10 +846,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="C6" s="1">
-        <v>1981</v>
+        <v>1970</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -716,13 +860,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -730,10 +871,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>87</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2995</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -741,30 +885,27 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1970</v>
       </c>
       <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1989</v>
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -772,39 +913,44 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1969</v>
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1989</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="2"/>
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="C13" s="1">
-        <v>1982</v>
+        <v>1969</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -812,21 +958,27 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1964</v>
+        <v>6</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>0</v>
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="C15" s="1">
-        <v>1969</v>
+        <v>1982</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
@@ -834,13 +986,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1964</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
@@ -848,10 +1000,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>0</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C17" s="1">
-        <v>1979</v>
+        <v>1969</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
@@ -859,10 +1014,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1971</v>
+        <v>43</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
@@ -870,10 +1028,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
       </c>
       <c r="C19" s="1">
-        <v>1972</v>
+        <v>1979</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
@@ -881,24 +1042,27 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>65</v>
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>97</v>
       </c>
       <c r="C20" s="1">
-        <v>1979</v>
+        <v>1971</v>
       </c>
       <c r="D20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>72</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="C21" s="1">
-        <v>1979</v>
+        <v>1993</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
@@ -906,10 +1070,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>98</v>
       </c>
       <c r="C22" s="1">
-        <v>1982</v>
+        <v>1972</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
@@ -917,10 +1084,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2</v>
+        <v>64</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C23" s="1">
-        <v>1987</v>
+        <v>1979</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
@@ -928,10 +1098,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
       </c>
       <c r="C24" s="1">
-        <v>1986</v>
+        <v>1979</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
@@ -939,13 +1112,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="C25" s="1">
-        <v>1966</v>
+        <v>1986</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
@@ -953,10 +1126,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C26" s="1">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
@@ -964,10 +1140,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1970</v>
+        <v>76</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
@@ -975,10 +1154,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>101</v>
       </c>
       <c r="C28" s="1">
-        <v>2015</v>
+        <v>1987</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
@@ -986,13 +1168,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C29" s="1">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
@@ -1000,10 +1182,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>104</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C30" s="1">
-        <v>1969</v>
+        <v>1981</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
@@ -1011,13 +1196,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>50</v>
+        <v>26</v>
+      </c>
+      <c r="B31" t="s">
+        <v>102</v>
       </c>
       <c r="C31" s="1">
-        <v>1971</v>
+        <v>1986</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
@@ -1025,10 +1210,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>21</v>
+        <v>48</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1966</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
@@ -1036,13 +1224,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>21</v>
+        <v>113</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1992</v>
       </c>
       <c r="D33" t="b">
         <v>1</v>
@@ -1050,13 +1238,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>21</v>
+        <v>90</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1984</v>
       </c>
       <c r="D34" t="b">
         <v>1</v>
@@ -1064,10 +1252,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>68</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C35" s="1">
-        <v>1970</v>
+        <v>1979</v>
       </c>
       <c r="D35" t="b">
         <v>1</v>
@@ -1075,13 +1266,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>22</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>63</v>
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
       </c>
       <c r="C36" s="1">
-        <v>1975</v>
+        <v>1979</v>
       </c>
       <c r="D36" t="b">
         <v>1</v>
@@ -1089,13 +1280,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1970</v>
       </c>
       <c r="D37" t="b">
         <v>1</v>
@@ -1103,13 +1294,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>46</v>
+        <v>3</v>
+      </c>
+      <c r="B38" t="s">
+        <v>107</v>
       </c>
       <c r="C38" s="1">
-        <v>1970</v>
+        <v>2015</v>
       </c>
       <c r="D38" t="b">
         <v>1</v>
@@ -1117,10 +1308,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>66</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="C39" s="1">
-        <v>1969</v>
+        <v>1978</v>
       </c>
       <c r="D39" t="b">
         <v>1</v>
@@ -1128,10 +1322,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>21</v>
+        <v>70</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1974</v>
       </c>
       <c r="D40" t="b">
         <v>1</v>
@@ -1139,10 +1336,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
       </c>
       <c r="C41" s="1">
-        <v>1979</v>
+        <v>1969</v>
       </c>
       <c r="D41" t="b">
         <v>1</v>
@@ -1150,13 +1350,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C42" s="1">
-        <v>2006</v>
+        <v>1968</v>
       </c>
       <c r="D42" t="b">
         <v>1</v>
@@ -1164,40 +1364,237 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1971</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1985</v>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="1">
+        <v>1969</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1989</v>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B56" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C56" s="1">
         <v>1975</v>
       </c>
-      <c r="D43" t="b">
+      <c r="D56" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
-    <hyperlink ref="B9" r:id="rId2" display="mailto:Rxbras@gmail.com" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
-    <hyperlink ref="B33" r:id="rId3" display="mailto:christopher.pavasaris@gmail.com" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
-    <hyperlink ref="B34" r:id="rId4" display="mailto:hll.reed01@gmail.com" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
-    <hyperlink ref="B37" r:id="rId5" display="mailto:adam@odysseyteencamp.com" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
-    <hyperlink ref="B16" r:id="rId6" display="mailto:michael.estep@acps.k12.va.us" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
-    <hyperlink ref="B38" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
-    <hyperlink ref="B12" r:id="rId8" display="mailto:artchristiani@gmail.com" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
-    <hyperlink ref="B25" r:id="rId9" display="mailto:Jlmorgan3@icloud.com" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
-    <hyperlink ref="B31" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
-    <hyperlink ref="B10" r:id="rId11" display="mailto:bcarignan85@gmail.com" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
-    <hyperlink ref="B43" r:id="rId12" display="mailto:martha529@aol.com" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
-    <hyperlink ref="B42" r:id="rId13" display="mailto:jason.derek.ward@gmail.com" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
+    <hyperlink ref="B11" r:id="rId2" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
+    <hyperlink ref="B45" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
+    <hyperlink ref="B46" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
+    <hyperlink ref="B49" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
+    <hyperlink ref="B18" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
+    <hyperlink ref="B50" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
+    <hyperlink ref="B14" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
+    <hyperlink ref="B32" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
+    <hyperlink ref="B43" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
+    <hyperlink ref="B56" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+    <hyperlink ref="B55" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
     <hyperlink ref="B2" r:id="rId14" display="mailto:louabare@yahoo.com" xr:uid="{8869974B-11E2-4A99-8438-9F9B8ABEB9F6}"/>
-    <hyperlink ref="B11" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
-    <hyperlink ref="B36" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
-    <hyperlink ref="B20" r:id="rId17" display="mailto:Drjpkonecny@gmail.com" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
-    <hyperlink ref="B29" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
+    <hyperlink ref="B13" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
+    <hyperlink ref="B48" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
+    <hyperlink ref="B23" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
+    <hyperlink ref="B39" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
+    <hyperlink ref="B35" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
+    <hyperlink ref="B40" r:id="rId20" xr:uid="{53A4A1D2-46D5-45C1-BB62-DA92169DD070}"/>
+    <hyperlink ref="B21" r:id="rId21" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
+    <hyperlink ref="B52" r:id="rId22" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
+    <hyperlink ref="B29" r:id="rId23" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
+    <hyperlink ref="B53" r:id="rId24" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
+    <hyperlink ref="B42" r:id="rId25" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
+    <hyperlink ref="B25" r:id="rId26" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
+    <hyperlink ref="B5" r:id="rId27" display="mailto:patrick@drpflexpak.com" xr:uid="{37F7977A-EC68-4733-8738-6C53C959B816}"/>
+    <hyperlink ref="B8" r:id="rId28" display="mailto:cwb84122@gmail.com" xr:uid="{A209B655-7CEF-4F8D-BFEE-DFB49C33870B}"/>
+    <hyperlink ref="B34" r:id="rId29" display="mailto:Npmyers@sbcglobal.net" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
+    <hyperlink ref="B6" r:id="rId30" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
+    <hyperlink ref="B17" r:id="rId31" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
+    <hyperlink ref="B26" r:id="rId32" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
+    <hyperlink ref="B30" r:id="rId33" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
+    <hyperlink ref="B27" r:id="rId34" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
+    <hyperlink ref="B44" r:id="rId35" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
+    <hyperlink ref="B33" r:id="rId36" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId19"/>
+  <pageSetup orientation="portrait" r:id="rId37"/>
 </worksheet>
 </file>
--- a/UConnBleedBlue/wwwroot/players/Players.xlsx
+++ b/UConnBleedBlue/wwwroot/players/Players.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\players\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391DE659-D108-454A-A60E-0B8F84E79AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073AF5E6-65AE-45AD-B8B1-CFC34105F6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F83266A-41F9-4FA3-9290-1EB5622BBFC1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="126">
   <si>
     <t>Demers, Kenny</t>
   </si>
@@ -378,6 +378,42 @@
   </si>
   <si>
     <t>Dmurphy287@charter.net</t>
+  </si>
+  <si>
+    <t>Corbo, Joe</t>
+  </si>
+  <si>
+    <t>joecorbo@icloud.com</t>
+  </si>
+  <si>
+    <t>Dunn, Steven</t>
+  </si>
+  <si>
+    <t>lostdogs@charter.net</t>
+  </si>
+  <si>
+    <t>DeGraffe, Herbert Dr</t>
+  </si>
+  <si>
+    <t>hdegraffe@gmail.com</t>
+  </si>
+  <si>
+    <t>Langley, Brian</t>
+  </si>
+  <si>
+    <t>langer0125@gmail.com</t>
+  </si>
+  <si>
+    <t>Thomas, Noel</t>
+  </si>
+  <si>
+    <t>Ntjr05@gmail.com</t>
+  </si>
+  <si>
+    <t>Sinay, Greg</t>
+  </si>
+  <si>
+    <t>gregsinay3@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -762,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F97E2D-D2EE-4E19-AA28-ED70E4256082}">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -918,8 +954,8 @@
       <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>21</v>
+      <c r="C11" s="1">
+        <v>1999</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -971,42 +1007,42 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1974</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C16" s="1">
         <v>1982</v>
       </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1964</v>
-      </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>0</v>
+      <c r="A17" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="C17" s="1">
-        <v>1969</v>
+        <v>1977</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
@@ -1014,13 +1050,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1964</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
@@ -1028,13 +1064,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" t="s">
-        <v>96</v>
+        <v>0</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C19" s="1">
-        <v>1979</v>
+        <v>1969</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
@@ -1042,13 +1078,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" t="s">
-        <v>97</v>
+        <v>116</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="C20" s="1">
-        <v>1971</v>
+        <v>1993</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
@@ -1056,13 +1092,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1993</v>
+        <v>44</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
@@ -1070,13 +1106,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C22" s="1">
-        <v>1972</v>
+        <v>1979</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
@@ -1084,13 +1120,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>65</v>
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>97</v>
       </c>
       <c r="C23" s="1">
-        <v>1979</v>
+        <v>1971</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
@@ -1098,13 +1134,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
-        <v>99</v>
+        <v>72</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="C24" s="1">
-        <v>1979</v>
+        <v>1993</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
@@ -1112,13 +1148,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>84</v>
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>98</v>
       </c>
       <c r="C25" s="1">
-        <v>1986</v>
+        <v>1972</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
@@ -1126,13 +1162,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="C26" s="1">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
@@ -1140,13 +1176,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="B27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1979</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
@@ -1154,13 +1190,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" t="s">
-        <v>101</v>
+        <v>83</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="C28" s="1">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
@@ -1168,13 +1204,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="C29" s="1">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
@@ -1182,13 +1218,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C30" s="1">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
@@ -1196,13 +1232,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="1">
-        <v>1986</v>
+        <v>76</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
@@ -1210,13 +1246,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>49</v>
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>101</v>
       </c>
       <c r="C32" s="1">
-        <v>1966</v>
+        <v>1987</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
@@ -1224,13 +1260,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C33" s="1">
-        <v>1992</v>
+        <v>1981</v>
       </c>
       <c r="D33" t="b">
         <v>1</v>
@@ -1238,13 +1274,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C34" s="1">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="D34" t="b">
         <v>1</v>
@@ -1252,13 +1288,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>69</v>
+        <v>26</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
       </c>
       <c r="C35" s="1">
-        <v>1979</v>
+        <v>1986</v>
       </c>
       <c r="D35" t="b">
         <v>1</v>
@@ -1266,13 +1302,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
+        <v>48</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="C36" s="1">
-        <v>1979</v>
+        <v>1966</v>
       </c>
       <c r="D36" t="b">
         <v>1</v>
@@ -1280,13 +1316,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" t="s">
-        <v>106</v>
+        <v>112</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="C37" s="1">
-        <v>1970</v>
+        <v>1992</v>
       </c>
       <c r="D37" t="b">
         <v>1</v>
@@ -1294,13 +1330,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" t="s">
-        <v>107</v>
+        <v>89</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="C38" s="1">
-        <v>2015</v>
+        <v>1984</v>
       </c>
       <c r="D38" t="b">
         <v>1</v>
@@ -1308,13 +1344,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C39" s="1">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="D39" t="b">
         <v>1</v>
@@ -1322,13 +1358,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>71</v>
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>103</v>
       </c>
       <c r="C40" s="1">
-        <v>1974</v>
+        <v>1979</v>
       </c>
       <c r="D40" t="b">
         <v>1</v>
@@ -1336,13 +1372,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C41" s="1">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D41" t="b">
         <v>1</v>
@@ -1350,13 +1386,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>81</v>
+        <v>3</v>
+      </c>
+      <c r="B42" t="s">
+        <v>107</v>
       </c>
       <c r="C42" s="1">
-        <v>1968</v>
+        <v>2015</v>
       </c>
       <c r="D42" t="b">
         <v>1</v>
@@ -1364,13 +1400,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C43" s="1">
-        <v>1971</v>
+        <v>1978</v>
       </c>
       <c r="D43" t="b">
         <v>1</v>
@@ -1378,13 +1414,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="C44" s="1">
-        <v>1985</v>
+        <v>1974</v>
       </c>
       <c r="D44" t="b">
         <v>1</v>
@@ -1392,13 +1428,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1969</v>
       </c>
       <c r="D45" t="b">
         <v>1</v>
@@ -1406,13 +1442,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>21</v>
+        <v>81</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1968</v>
       </c>
       <c r="D46" t="b">
         <v>1</v>
@@ -1420,13 +1456,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>13</v>
-      </c>
-      <c r="B47" t="s">
-        <v>110</v>
+        <v>15</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="C47" s="1">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D47" t="b">
         <v>1</v>
@@ -1434,13 +1470,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="C48" s="1">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="D48" t="b">
         <v>1</v>
@@ -1448,10 +1484,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>21</v>
@@ -1462,13 +1498,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50" s="1">
-        <v>1970</v>
+        <v>40</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D50" t="b">
         <v>1</v>
@@ -1476,13 +1512,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C51" s="1">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D51" t="b">
         <v>1</v>
@@ -1490,10 +1526,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C52" s="1">
         <v>1975</v>
@@ -1504,13 +1540,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" s="1">
-        <v>1989</v>
+        <v>42</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D53" t="b">
         <v>1</v>
@@ -1518,10 +1554,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>124</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="C54" s="1">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="D54" t="b">
         <v>1</v>
@@ -1529,13 +1568,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C55" s="1">
-        <v>2006</v>
+        <v>1970</v>
       </c>
       <c r="D55" t="b">
         <v>1</v>
@@ -1543,15 +1582,96 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" s="1">
+        <v>1969</v>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1975</v>
+      </c>
+      <c r="D58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1989</v>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1979</v>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>53</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B62" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C62" s="1">
         <v>1975</v>
       </c>
-      <c r="D56" t="b">
+      <c r="D62" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1559,42 +1679,48 @@
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{8227A597-9225-4357-B8B6-9F19CC6D2D47}"/>
     <hyperlink ref="B11" r:id="rId2" xr:uid="{C440EE30-529A-4080-AE83-A4A978C3E02B}"/>
-    <hyperlink ref="B45" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
-    <hyperlink ref="B46" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
-    <hyperlink ref="B49" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
-    <hyperlink ref="B18" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
-    <hyperlink ref="B50" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
+    <hyperlink ref="B49" r:id="rId3" xr:uid="{C5FAAB38-5F1C-4A08-8709-401E7E23E0D1}"/>
+    <hyperlink ref="B50" r:id="rId4" xr:uid="{109EA93A-660A-4099-B212-FD77BC4B5297}"/>
+    <hyperlink ref="B53" r:id="rId5" xr:uid="{4FC29F3F-346D-4C86-81DD-BA31CA08B134}"/>
+    <hyperlink ref="B21" r:id="rId6" xr:uid="{98703E9F-F4A5-4829-8BBF-B9F807C63E68}"/>
+    <hyperlink ref="B55" r:id="rId7" display="mailto:1photodog@gmail.com" xr:uid="{9E8BA56C-3438-4645-83BE-2770570162B4}"/>
     <hyperlink ref="B14" r:id="rId8" xr:uid="{804D2DB9-BDF1-463B-9BD3-ACBFC15F041A}"/>
-    <hyperlink ref="B32" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
-    <hyperlink ref="B43" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
+    <hyperlink ref="B36" r:id="rId9" xr:uid="{03952628-4855-439F-9B40-CAC6626447C4}"/>
+    <hyperlink ref="B47" r:id="rId10" display="mailto:npisciottano@hotmail.com" xr:uid="{781976BA-4287-4FD4-8728-D3D09F930C18}"/>
     <hyperlink ref="B12" r:id="rId11" xr:uid="{DF6F8079-E647-4079-9719-72DC2FF3791C}"/>
-    <hyperlink ref="B56" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
-    <hyperlink ref="B55" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
+    <hyperlink ref="B62" r:id="rId12" xr:uid="{6DF6CCA4-C8CA-41C8-BD42-527DBB5CB505}"/>
+    <hyperlink ref="B61" r:id="rId13" xr:uid="{ECCFE763-5E69-4122-B27B-DA1C21FADA86}"/>
     <hyperlink ref="B2" r:id="rId14" display="mailto:louabare@yahoo.com" xr:uid="{8869974B-11E2-4A99-8438-9F9B8ABEB9F6}"/>
     <hyperlink ref="B13" r:id="rId15" display="mailto:elizabeth.casarella@gmail.com" xr:uid="{C150E814-8C96-4E50-8A55-5EB3344749B1}"/>
-    <hyperlink ref="B48" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
-    <hyperlink ref="B23" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
-    <hyperlink ref="B39" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
-    <hyperlink ref="B35" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
-    <hyperlink ref="B40" r:id="rId20" xr:uid="{53A4A1D2-46D5-45C1-BB62-DA92169DD070}"/>
-    <hyperlink ref="B21" r:id="rId21" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
-    <hyperlink ref="B52" r:id="rId22" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
-    <hyperlink ref="B29" r:id="rId23" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
-    <hyperlink ref="B53" r:id="rId24" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
-    <hyperlink ref="B42" r:id="rId25" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
-    <hyperlink ref="B25" r:id="rId26" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
+    <hyperlink ref="B52" r:id="rId16" display="mailto:paul@levelbreaker.com" xr:uid="{9746CC3F-863E-4E18-931A-FADD4ED10BF2}"/>
+    <hyperlink ref="B26" r:id="rId17" xr:uid="{316BCF75-05DF-4572-9F46-9F76127C0677}"/>
+    <hyperlink ref="B43" r:id="rId18" display="mailto:dennis.p.oconnell@gmail.com" xr:uid="{57197F8F-1C51-4977-936A-74B15D239DF7}"/>
+    <hyperlink ref="B39" r:id="rId19" display="mailto:hef714@aol.com" xr:uid="{A4825BC7-F2DD-43E9-A39B-48544C54E403}"/>
+    <hyperlink ref="B44" r:id="rId20" xr:uid="{53A4A1D2-46D5-45C1-BB62-DA92169DD070}"/>
+    <hyperlink ref="B24" r:id="rId21" xr:uid="{A871275A-577B-4F01-A590-B30FBADA40A1}"/>
+    <hyperlink ref="B58" r:id="rId22" xr:uid="{7E7AC9EC-4484-43DC-8B81-7AA0BCCFA407}"/>
+    <hyperlink ref="B33" r:id="rId23" display="mailto:Gjhusky52@yahoo.com" xr:uid="{1F5D9E16-5BA9-4F8F-B8CF-14485F325E5D}"/>
+    <hyperlink ref="B59" r:id="rId24" display="mailto:s.vibberts@yahoo.com" xr:uid="{CD95CA65-C8C5-44B3-8AFC-2E088AEC194C}"/>
+    <hyperlink ref="B46" r:id="rId25" display="mailto:oldparsonage3@gmail.com" xr:uid="{DC8DA8C9-CCEA-4FC3-AA05-1EF34B65B0C1}"/>
+    <hyperlink ref="B28" r:id="rId26" xr:uid="{C2395B48-B35E-4045-A136-C8B31BE4A5FC}"/>
     <hyperlink ref="B5" r:id="rId27" display="mailto:patrick@drpflexpak.com" xr:uid="{37F7977A-EC68-4733-8738-6C53C959B816}"/>
     <hyperlink ref="B8" r:id="rId28" display="mailto:cwb84122@gmail.com" xr:uid="{A209B655-7CEF-4F8D-BFEE-DFB49C33870B}"/>
-    <hyperlink ref="B34" r:id="rId29" display="mailto:Npmyers@sbcglobal.net" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
+    <hyperlink ref="B38" r:id="rId29" display="mailto:Npmyers@sbcglobal.net" xr:uid="{46F1EE8C-941D-4D6B-A27A-3BDDA65A15CE}"/>
     <hyperlink ref="B6" r:id="rId30" xr:uid="{647703FF-1796-4612-923D-2A3CF89F5A46}"/>
-    <hyperlink ref="B17" r:id="rId31" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
-    <hyperlink ref="B26" r:id="rId32" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
-    <hyperlink ref="B30" r:id="rId33" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
-    <hyperlink ref="B27" r:id="rId34" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
-    <hyperlink ref="B44" r:id="rId35" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
-    <hyperlink ref="B33" r:id="rId36" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
+    <hyperlink ref="B19" r:id="rId31" xr:uid="{D4F421DD-A322-4F00-A209-B464A28664A6}"/>
+    <hyperlink ref="B30" r:id="rId32" xr:uid="{5FF15619-CFAB-48CB-8BF0-78013919701C}"/>
+    <hyperlink ref="B34" r:id="rId33" display="mailto:Kmills8080@gmail.com" xr:uid="{6653A4F2-00C8-4ACF-A9B2-950ABB23037C}"/>
+    <hyperlink ref="B31" r:id="rId34" xr:uid="{0F8932AA-3F92-4F04-A82F-C839649C3558}"/>
+    <hyperlink ref="B48" r:id="rId35" xr:uid="{74573551-A238-45F0-95FA-078470676D33}"/>
+    <hyperlink ref="B37" r:id="rId36" xr:uid="{F093A50A-9255-43F2-873A-E61FB97B7B6E}"/>
+    <hyperlink ref="B15" r:id="rId37" display="mailto:joecorbo@icloud.com" xr:uid="{9664FD56-34AE-4697-8A23-BBA8942C6ABA}"/>
+    <hyperlink ref="B20" r:id="rId38" display="mailto:lostdogs@charter.net" xr:uid="{95D046AE-D83E-4029-8E4D-F457CDD3F23E}"/>
+    <hyperlink ref="B17" r:id="rId39" xr:uid="{93D1D532-1D29-4735-B6C3-7B9B46F15302}"/>
+    <hyperlink ref="B29" r:id="rId40" display="mailto:langer0125@gmail.com" xr:uid="{EF3BA7C4-32BE-431A-9979-8B42711B0D73}"/>
+    <hyperlink ref="B56" r:id="rId41" display="mailto:Ntjr05@gmail.com" xr:uid="{38DDEC56-F2AD-4C66-8377-3BFC9B7BDDB9}"/>
+    <hyperlink ref="B54" r:id="rId42" display="mailto:gregsinay3@gmail.com" xr:uid="{004C878C-63EB-40FC-B549-87CFABDE66E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId37"/>
+  <pageSetup orientation="portrait" r:id="rId43"/>
 </worksheet>
 </file>